--- a/product_surveys/002_perfume_box--product_surveys.xlsx
+++ b/product_surveys/002_perfume_box--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,9 +440,9 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>What is the name of this perfume box?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>What category does this perfume box belong to?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Describe the product in 5-10 sentences.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>What is the ID of this perfume box?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_category</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>What is the category for this perfume box?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_is_for_sale</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>Is the product for sale?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_visit_frequency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>How often do you visit our perfume store?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_size</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>What is the size of this perfume box?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_color</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>What is the color of this perfume box?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -730,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,6 +786,193 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>form_visit_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>once_a_week</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Once a week</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>form_visit_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2-3_times_a_week</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2-3 times a week</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>form_visit_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>form_visit_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>form_size_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>form_size_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>form_size_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>form_color_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>form_color_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>form_color_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>form_color_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
